--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B2" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B5" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B6" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B7" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B28" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B29" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B38" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B52" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B53" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -1693,7 +1693,7 @@
         <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -1237,7 +1237,7 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B23" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B24" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -436,28 +436,28 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer)</v>
+        <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B2" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
+        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Madonna</v>
+        <v>Danna</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,33 +469,33 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
+        <v>DANNA - MOVIE STAR - Danna</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B3" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
+        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Freya Ridings</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,33 +507,33 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle)</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B4" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
+        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Celine Dion</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,33 +545,33 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B5" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
+        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Peter Gabriel</v>
+        <v>Cannons</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,33 +583,33 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
+        <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
+        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Beck</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,33 +621,33 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
+        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Jessie Ware - Superbloom</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
+        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Jessie Ware</v>
+        <v>Frank Walker and salem ilese</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,33 +659,33 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Jessie Ware - Superbloom - Jessie Ware</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B8" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
+        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,33 +697,33 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer)</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B9" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
+        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>ERNEST</v>
+        <v>Digster Pop Music</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,33 +735,33 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
+        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Beck</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,33 +773,33 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Beck - Ride Lonesome (Audio) - Beck</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
+        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Dean Lewis</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,33 +811,33 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video)</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B12" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
+        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Bella White</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,33 +849,33 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Kip Moore - Faith In The Wind (Official)</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
+        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Kip Moore</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,33 +887,33 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
+        <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B14" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
+        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Madonna</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,21 +925,21 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
+        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B15" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
+        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -951,7 +951,7 @@
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Ben Gallaher</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,21 +963,21 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
+        <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B16" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
+        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -989,7 +989,7 @@
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Reservoir Recordings</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,21 +1001,21 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
+        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video)</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B17" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
+        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1027,7 +1027,7 @@
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Johnny Orlando</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,21 +1039,21 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B18" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
+        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1065,7 +1065,7 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Tyla</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,21 +1077,21 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
+        <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B19" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
+        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1103,7 +1103,7 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,33 +1115,33 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
+        <v>Jessie Ware - Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video)</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
+        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Lana Del Rey</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,33 +1153,33 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Loreen - True Love (Official Video)</v>
+        <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B21" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
+        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Loreen</v>
+        <v>ERNEST</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,33 +1191,33 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Loreen - True Love (Official Video) - Loreen</v>
+        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B22" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
+        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Bonnie Tyler</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,21 +1229,21 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B23" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
+        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1255,7 +1255,7 @@
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Tenille Townes</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,21 +1267,21 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Cream - White Room [Official Lyric Video]</v>
+        <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
+        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1293,7 +1293,7 @@
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Cream - Band and 2 more</v>
+        <v>Bella White</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,21 +1305,21 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
+        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY</v>
+        <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B25" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
+        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1331,7 +1331,7 @@
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Danna</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,21 +1343,21 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
+        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
+        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1369,7 +1369,7 @@
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>OneRepublic</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,21 +1381,21 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video)</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B27" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
+        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1407,7 +1407,7 @@
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>The Revivalists</v>
+        <v>Ben Gallaher</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,33 +1419,33 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal)</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
+        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>James Smith</v>
+        <v>Reservoir Recordings</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,33 +1457,33 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
+        <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
+        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Holly Humberstone</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,33 +1495,33 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
+        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B30" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
+        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Ava Max</v>
+        <v>Tyla</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,33 +1533,33 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>John Summit - STATUS:AWAY</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
+        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>John Summit</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,33 +1571,33 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>John Summit - STATUS:AWAY - John Summit</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
+        <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
+        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Ava Max</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,33 +1609,33 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
+        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>DANNA - AGAIN (Lyric Video)</v>
+        <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
+        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Danna</v>
+        <v>Loreen</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,33 +1647,33 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
+        <v>Loreen - True Love (Official Video) - Loreen</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
+        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Conan Gray</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,33 +1685,33 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Temples - Vendetta (Official Video)</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B35" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
+        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>TemplesOfficial</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,33 +1723,33 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Laufey - Madwoman (Official Music Video)</v>
+        <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B36" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
+        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Laufey</v>
+        <v>Cream - Band and 2 more</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,33 +1761,33 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
+        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Bleachers - the van (Official Music Video)</v>
+        <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B37" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
+        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>bleachers</v>
+        <v>Danna</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,33 +1799,33 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Bleachers - the van (Official Music Video) - bleachers</v>
+        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B38" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
+        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Nothing But Thieves</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,33 +1837,33 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
+        <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
+        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>LANY</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,33 +1875,33 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
+        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
+        <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B40" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
+        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>James Smith</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,33 +1913,33 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B41" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
+        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,33 +1951,33 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
+        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>keshi and AT&amp;T</v>
+        <v>Ava Max</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,33 +1989,33 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
+        <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B43" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
+        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Kygo and carter faith</v>
+        <v>John Summit</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,33 +2027,33 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
+        <v>John Summit - STATUS:AWAY - John Summit</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video)</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B44" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
+        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>florencemachine</v>
+        <v>Ava Max</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,33 +2065,33 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
+        <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
+        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Scorpions</v>
+        <v>Danna</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,33 +2103,33 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
+        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B46" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
+        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Holly Humberstone</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,33 +2141,33 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>HAUSER - Pavane</v>
+        <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
+        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>HAUSER</v>
+        <v>TemplesOfficial</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,33 +2179,33 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>HAUSER - Pavane - HAUSER</v>
+        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video)</v>
+        <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
+        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Holly Humberstone</v>
+        <v>Laufey</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,33 +2217,33 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
+        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>YES - Aurora (Official Video)</v>
+        <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
+        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>yesofficial and InsideOutMusicTV</v>
+        <v>bleachers</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,33 +2255,33 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
+        <v>Bleachers - the van (Official Music Video) - bleachers</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video)</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B50" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
+        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Mae Muller</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,33 +2293,33 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Dead Pony - Freak Like Me (Official Music Video)</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
+        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Dead Pony</v>
+        <v>LANY</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,33 +2331,33 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Dead Pony - Freak Like Me (Official Music Video) - Dead Pony</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B52" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
+        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,33 +2369,33 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023) - Nothing But Thieves</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B53" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
+        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,21 +2407,21 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish) - Jennifer Lopez</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>kenzie - where do we go</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B54" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
+        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2433,7 +2433,7 @@
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>kenzie</v>
+        <v>keshi and AT&amp;T</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,21 +2445,21 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>kenzie - where do we go - kenzie</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Foo Fighters - Of All People (Lyric Video)</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B55" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
+        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2471,7 +2471,7 @@
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Foo Fighters</v>
+        <v>Kygo and carter faith</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,21 +2483,21 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Foo Fighters - Of All People (Lyric Video) - Foo Fighters</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
+        <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B56" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
+        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2509,7 +2509,7 @@
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Laufey</v>
+        <v>florencemachine</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,21 +2521,21 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Laufey - Madwoman (Official Lyric Video with Chords) - Laufey</v>
+        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Ella Langley - Somethin' Simple (Official Audio)</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B57" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
+        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2547,7 +2547,7 @@
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Ella Langley</v>
+        <v>Scorpions</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,21 +2559,21 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Ella Langley - Somethin' Simple (Official Audio) - Ella Langley</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B58" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
+        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2585,7 +2585,7 @@
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Mei Semones</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,21 +2597,21 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer) - Mei Semones</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
+        <v>HAUSER - Pavane</v>
       </c>
       <c r="B59" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
+        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2623,7 +2623,7 @@
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Evanescence</v>
+        <v>HAUSER</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,21 +2635,21 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Evanescence - Who Will You Follow (Official Lyric Video) - Evanescence</v>
+        <v>HAUSER - Pavane - HAUSER</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>elijah woods - DNA (Treehouse Sessions)</v>
+        <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B60" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
+        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2661,7 +2661,7 @@
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>elijah woods</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,21 +2673,21 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>elijah woods - DNA (Treehouse Sessions) - elijah woods</v>
+        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>colby! - Who's Your Angel Now (Official Music Video)</v>
+        <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B61" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
+        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2699,7 +2699,7 @@
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>colby!</v>
+        <v>yesofficial and InsideOutMusicTV</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,21 +2711,21 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>colby! - Who's Your Angel Now (Official Music Video) - colby!</v>
+        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
+        <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
+        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>The Chainsmokers</v>
+        <v>Mae Muller</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,21 +2749,21 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer) - The Chainsmokers</v>
+        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>aron! - Foolsong (Guitar)</v>
+        <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
+        <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2775,7 +2775,7 @@
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>aron!</v>
+        <v>Dead Pony</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,21 +2787,21 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>aron! - Foolsong (Guitar) - aron!</v>
+        <v>Dead Pony - Freak Like Me (Official Music Video) - Dead Pony</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Owen Riegling - Anything But Me</v>
+        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B64" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
+        <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2813,7 +2813,7 @@
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Owen Riegling</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,21 +2825,21 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Owen Riegling - Anything But Me - Owen Riegling</v>
+        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
+        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B65" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
+        <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2851,7 +2851,7 @@
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Lainey Wilson and Nova's Red Room</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,33 +2863,33 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session - Lainey Wilson and Nova's Red Room</v>
+        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Teddy Swims - Mr. Know It All</v>
+        <v>kenzie - where do we go</v>
       </c>
       <c r="B66" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
+        <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Teddy Swims</v>
+        <v>kenzie</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,33 +2901,33 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Teddy Swims - Mr. Know It All - Teddy Swims</v>
+        <v>kenzie - where do we go - kenzie</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
+        <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
+        <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>BEAUTY SCHOOL DROPOUT</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,33 +2939,33 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video) - BEAUTY SCHOOL DROPOUT</v>
+        <v>Foo Fighters - Of All People (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
+        <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B68" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
+        <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>twenty one pilots and AT&amp;T</v>
+        <v>Laufey</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,33 +2977,33 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
+        <v>Laufey - Madwoman (Official Lyric Video with Chords) - Laufey</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Sunday (1994) - Shame (Official Video)</v>
+        <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
+        <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Sunday (1994)</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,21 +3015,21 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Sunday (1994) - Shame (Official Video) - Sunday (1994)</v>
+        <v>Ella Langley - Somethin' Simple (Official Audio) - Ella Langley</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
+        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B70" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
+        <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3041,7 +3041,7 @@
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>twenty one pilots and AT&amp;T</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,21 +3053,21 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
+        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer) - Mei Semones</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
+        <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
+        <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3079,7 +3079,7 @@
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Freya Skye</v>
+        <v>Evanescence</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,21 +3091,21 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London) - Freya Skye</v>
+        <v>Evanescence - Who Will You Follow (Official Lyric Video) - Evanescence</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
+        <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B72" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
+        <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3117,7 +3117,7 @@
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Bryan Adams</v>
+        <v>elijah woods</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,21 +3129,21 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film - Bryan Adams</v>
+        <v>elijah woods - DNA (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>We Three - New Zealand (Live Sessions)</v>
+        <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
+        <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3155,7 +3155,7 @@
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>We Three</v>
+        <v>colby!</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,21 +3167,21 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>We Three - New Zealand (Live Sessions) - We Three</v>
+        <v>colby! - Who's Your Angel Now (Official Music Video) - colby!</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
+        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
+        <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3193,7 +3193,7 @@
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Dermot Kennedy</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,21 +3205,21 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Bebe Rexha - Hysteria (Official Visual)</v>
+        <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B75" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
+        <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3231,7 +3231,7 @@
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Bebe Rexha</v>
+        <v>aron!</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,21 +3243,21 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Bebe Rexha - Hysteria (Official Visual) - Bebe Rexha</v>
+        <v>aron! - Foolsong (Guitar) - aron!</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
+        <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B76" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
+        <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3269,7 +3269,7 @@
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,33 +3281,33 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>The Lemon Twigs - 2 or 3 (Official Video) - The Lemon Twigs</v>
+        <v>Owen Riegling - Anything But Me - Owen Riegling</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>METTE - COMING OF AGE (Official Video)</v>
+        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
+        <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>METTE</v>
+        <v>Lainey Wilson and Nova's Red Room</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,33 +3319,33 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>METTE - COMING OF AGE (Official Video) - METTE</v>
+        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session - Lainey Wilson and Nova's Red Room</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Saint Harison - stuck (Official Music Video)</v>
+        <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
+        <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Saint Harison</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,33 +3357,33 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Saint Harison - stuck (Official Music Video) - Saint Harison</v>
+        <v>Teddy Swims - Mr. Know It All - Teddy Swims</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Newdad - Kick The Curb</v>
+        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
+        <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>NewDad</v>
+        <v>BEAUTY SCHOOL DROPOUT</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,33 +3395,33 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Newdad - Kick The Curb - NewDad</v>
+        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video) - BEAUTY SCHOOL DROPOUT</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>DANNA - LUCID (Visualizer)</v>
+        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
+        <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Danna</v>
+        <v>twenty one pilots and AT&amp;T</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,33 +3433,33 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>DANNA - LUCID (Visualizer) - Danna</v>
+        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
+        <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
+        <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>florencemachine</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,21 +3471,21 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Florence + The Machine - You Can Have It All (Visualiser) - florencemachine</v>
+        <v>Sunday (1994) - Shame (Official Video) - Sunday (1994)</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
+        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
+        <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3497,7 +3497,7 @@
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>HYBE LABELS</v>
+        <v>twenty one pilots and AT&amp;T</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,21 +3509,21 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>BTS (방탄소년단) 'Hooligan' Official MV - HYBE LABELS</v>
+        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
+        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
+        <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3535,7 +3535,7 @@
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Kungs</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,21 +3547,21 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Kungs, Stevie Appleton - Body Talk (Visualizer) - Kungs</v>
+        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London) - Freya Skye</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
+        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
+        <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3573,7 +3573,7 @@
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Charlie Puth</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,21 +3585,21 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint - Charlie Puth</v>
+        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film - Bryan Adams</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
+        <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
+        <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3611,7 +3611,7 @@
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Nothing But Thieves</v>
+        <v>We Three</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,21 +3623,21 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Nothing But Thieves - There Was Sun (Official Audio) - Nothing But Thieves</v>
+        <v>We Three - New Zealand (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
+        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
+        <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3649,7 +3649,7 @@
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>SIENNA SPIRO and The Jonathan Ross Show</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,21 +3661,21 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show - SIENNA SPIRO and The Jonathan Ross Show</v>
+        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
+        <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
+        <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3687,7 +3687,7 @@
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Madison Cunningham</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,21 +3699,21 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Madison Cunningham - Hospital (Live at Big Ears Festival) - Madison Cunningham</v>
+        <v>Bebe Rexha - Hysteria (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
+        <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
+        <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3725,7 +3725,7 @@
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Armin van Buuren</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,21 +3737,21 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>The Lemon Twigs - 2 or 3 (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Sabrina Carpenter - House Tour (Official Video)</v>
+        <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
+        <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3763,7 +3763,7 @@
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>METTE</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,33 +3775,33 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Sabrina Carpenter - House Tour (Official Video) - Sabrina Carpenter</v>
+        <v>METTE - COMING OF AGE (Official Video) - METTE</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Nothing But Thieves - Free If We Want It (Official Audio)</v>
+        <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
+        <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,33 +3813,33 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Nothing But Thieves - Free If We Want It (Official Audio) - Nothing But Thieves</v>
+        <v>Saint Harison - stuck (Official Music Video) - Saint Harison</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO)</v>
+        <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B91" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
+        <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Ocean Alley</v>
+        <v>NewDad</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,33 +3851,33 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO) - Ocean Alley</v>
+        <v>Newdad - Kick The Curb - NewDad</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios)</v>
+        <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B92" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
+        <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>RAYE</v>
+        <v>Danna</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,33 +3889,33 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios) - RAYE</v>
+        <v>DANNA - LUCID (Visualizer) - Danna</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Take That - You're A Superstar (Lyric Video)</v>
+        <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B93" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
+        <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Take That</v>
+        <v>florencemachine</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,33 +3927,33 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Take That - You're A Superstar (Lyric Video) - Take That</v>
+        <v>Florence + The Machine - You Can Have It All (Visualiser) - florencemachine</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B94" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
+        <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Armik</v>
+        <v>HYBE LABELS</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,33 +3965,33 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>BTS (방탄소년단) 'Hooligan' Official MV - HYBE LABELS</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video)</v>
+        <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B95" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
+        <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Switchfoot</v>
+        <v>Kungs</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,33 +4003,33 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video) - Switchfoot</v>
+        <v>Kungs, Stevie Appleton - Body Talk (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour)</v>
+        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B96" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
+        <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Peter Gabriel</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,33 +4041,33 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour) - Peter Gabriel</v>
+        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint - Charlie Puth</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Sarah Julia - Bigger Picture (Official Lyric Video)</v>
+        <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B97" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
+        <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Sarah Julia</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,33 +4079,33 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Sarah Julia - Bigger Picture (Official Lyric Video) - Sarah Julia</v>
+        <v>Nothing But Thieves - There Was Sun (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Chris Norman - Addicted To Love (Official Video)</v>
+        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B98" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
+        <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Chris Norman</v>
+        <v>SIENNA SPIRO and The Jonathan Ross Show</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,33 +4117,33 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Chris Norman - Addicted To Love (Official Video) - Chris Norman</v>
+        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show - SIENNA SPIRO and The Jonathan Ross Show</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
+        <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B99" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
+        <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Alan Walker</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,33 +4155,33 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video) - Alan Walker</v>
+        <v>Madison Cunningham - Hospital (Live at Big Ears Festival) - Madison Cunningham</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
+        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B100" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
+        <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Charlie Puth</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,33 +4193,33 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
+        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
+        <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Miley Cyrus</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>Sabrina Carpenter - House Tour (Official Video) - Sabrina Carpenter</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -895,7 +895,7 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B14" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B17" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B18" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B19" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B40" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B41" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B50" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B64" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B65" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -1693,7 +1693,7 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B35" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B36" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -477,7 +477,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B12" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B16" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B38" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B46" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B57" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>HAUSER - Pavane</v>
       </c>
       <c r="B59" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -591,7 +591,7 @@
         <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -1541,7 +1541,7 @@
         <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B54" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B77" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B78" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B80" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -439,19 +439,19 @@
         <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,19 +477,19 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B3" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,19 +515,19 @@
         <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B4" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,19 +553,19 @@
         <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B5" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,19 +591,19 @@
         <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,19 +629,19 @@
         <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,19 +667,19 @@
         <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B8" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,19 +705,19 @@
         <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B9" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,19 +743,19 @@
         <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,19 +781,19 @@
         <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,19 +819,19 @@
         <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B12" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,19 +857,19 @@
         <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,19 +895,19 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B14" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,19 +933,19 @@
         <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,19 +971,19 @@
         <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B16" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,19 +1009,19 @@
         <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B17" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,19 +1047,19 @@
         <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B18" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,19 +1085,19 @@
         <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B19" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,19 +1123,19 @@
         <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,19 +1161,19 @@
         <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B21" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,19 +1199,19 @@
         <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B22" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,19 +1237,19 @@
         <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,19 +1275,19 @@
         <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,19 +1313,19 @@
         <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B25" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,19 +1351,19 @@
         <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,19 +1389,19 @@
         <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B27" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,19 +1427,19 @@
         <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,19 +1465,19 @@
         <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,19 +1503,19 @@
         <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B30" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,19 +1541,19 @@
         <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,19 +1579,19 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,19 +1617,19 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,19 +1655,19 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,19 +1693,19 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B35" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,19 +1731,19 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B36" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,19 +1769,19 @@
         <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B37" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,19 +1807,19 @@
         <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B38" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,19 +1845,19 @@
         <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,19 +1883,19 @@
         <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B40" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,19 +1921,19 @@
         <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B41" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,19 +1959,19 @@
         <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,19 +1997,19 @@
         <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B43" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,19 +2035,19 @@
         <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B44" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,19 +2073,19 @@
         <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,19 +2111,19 @@
         <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B46" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,19 +2149,19 @@
         <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,19 +2187,19 @@
         <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,19 +2225,19 @@
         <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,19 +2263,19 @@
         <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B50" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,19 +2301,19 @@
         <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,19 +2339,19 @@
         <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B52" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,19 +2377,19 @@
         <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B53" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,19 +2415,19 @@
         <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B54" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,19 +2453,19 @@
         <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,19 +2491,19 @@
         <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,19 +2529,19 @@
         <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B57" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,19 +2567,19 @@
         <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,19 +2605,19 @@
         <v>HAUSER - Pavane</v>
       </c>
       <c r="B59" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,19 +2643,19 @@
         <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,19 +2681,19 @@
         <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,19 +2719,19 @@
         <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,19 +2757,19 @@
         <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,19 +2795,19 @@
         <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B64" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,19 +2833,19 @@
         <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B65" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,19 +2871,19 @@
         <v>kenzie - where do we go</v>
       </c>
       <c r="B66" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,19 +2909,19 @@
         <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,19 +2947,19 @@
         <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B68" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,19 +2985,19 @@
         <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,19 +3023,19 @@
         <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B70" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,19 +3061,19 @@
         <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,19 +3099,19 @@
         <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B72" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,19 +3137,19 @@
         <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,19 +3175,19 @@
         <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,19 +3213,19 @@
         <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B75" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,19 +3251,19 @@
         <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B76" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,19 +3289,19 @@
         <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,19 +3327,19 @@
         <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,19 +3365,19 @@
         <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,19 +3403,19 @@
         <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,19 +3441,19 @@
         <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,19 +3479,19 @@
         <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,19 +3517,19 @@
         <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,19 +3555,19 @@
         <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,19 +3593,19 @@
         <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,19 +3631,19 @@
         <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,19 +3669,19 @@
         <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,19 +3707,19 @@
         <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,19 +3745,19 @@
         <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,19 +3783,19 @@
         <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,19 +3821,19 @@
         <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,19 +3859,19 @@
         <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,19 +3897,19 @@
         <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,19 +3935,19 @@
         <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,19 +3973,19 @@
         <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,19 +4011,19 @@
         <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,19 +4049,19 @@
         <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,19 +4087,19 @@
         <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,19 +4125,19 @@
         <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,19 +4163,19 @@
         <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,19 +4201,19 @@
         <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B2" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B3" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B4" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B5" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B8" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B9" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B12" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B14" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B16" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B17" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B18" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B19" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B21" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B22" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B25" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B27" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B30" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B35" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B36" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B37" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B38" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B40" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B41" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B43" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B44" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B46" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B50" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B52" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B53" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B54" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B57" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>HAUSER - Pavane</v>
       </c>
       <c r="B59" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B64" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B65" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>kenzie - where do we go</v>
       </c>
       <c r="B66" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B68" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B70" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B72" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B75" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B76" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B77" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B78" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B80" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B82" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B96" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B97" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B98" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B99" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B100" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -515,7 +515,7 @@
         <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B4" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B5" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B8" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B9" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B12" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B16" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B35" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B36" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B38" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B57" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>HAUSER - Pavane</v>
       </c>
       <c r="B59" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -477,7 +477,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B3" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B46" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -591,7 +591,7 @@
         <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -1541,7 +1541,7 @@
         <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B54" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -439,19 +439,19 @@
         <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B2" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1769,19 +1769,19 @@
         <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B37" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2073,19 +2073,19 @@
         <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2339,19 +2339,19 @@
         <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B52" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,19 +2377,19 @@
         <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B53" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B2" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B3" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B4" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B5" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B8" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B9" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B12" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B14" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B16" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B17" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B18" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B19" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B21" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B22" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B25" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B27" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B30" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B35" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B36" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B37" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B38" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B40" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B41" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B43" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B44" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B46" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B50" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B52" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B53" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B54" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B57" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>HAUSER - Pavane</v>
       </c>
       <c r="B59" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B64" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B65" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>kenzie - where do we go</v>
       </c>
       <c r="B66" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B68" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B70" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B72" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B75" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B76" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B2" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B3" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B4" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B5" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B8" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B9" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B12" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B14" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B16" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B17" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B18" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B19" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B21" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B22" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B25" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B27" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B30" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B35" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B36" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B37" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B38" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B40" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B41" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B43" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B44" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B46" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B50" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B52" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B53" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B54" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B57" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>HAUSER - Pavane</v>
       </c>
       <c r="B59" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B64" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B65" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>kenzie - where do we go</v>
       </c>
       <c r="B66" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B68" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B70" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B72" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B75" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B76" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B77" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B78" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B80" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B82" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B96" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B97" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B98" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B99" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B100" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -895,7 +895,7 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B14" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B17" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B18" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B19" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B50" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B2" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B3" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B4" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B5" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B8" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B9" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B12" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B14" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B16" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B17" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B18" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B19" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B21" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B22" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B25" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B27" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B30" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B35" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B36" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B37" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B38" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B40" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B41" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B43" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B44" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B46" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B50" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B52" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B53" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B54" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B57" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>HAUSER - Pavane</v>
       </c>
       <c r="B59" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B64" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B65" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>kenzie - where do we go</v>
       </c>
       <c r="B66" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B68" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B70" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B72" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B75" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B76" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B2" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B3" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B4" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B5" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B8" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B9" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B12" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B14" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B16" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B17" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B18" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B19" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B21" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B22" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B25" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B27" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B30" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B35" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B36" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B37" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B38" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B40" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B41" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B43" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B44" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B46" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B50" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B52" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B53" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B54" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B57" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>HAUSER - Pavane</v>
       </c>
       <c r="B59" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B64" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B65" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>kenzie - where do we go</v>
       </c>
       <c r="B66" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B68" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B70" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B72" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B75" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B76" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B77" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B78" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B80" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B82" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B96" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B97" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B98" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B99" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B100" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -857,7 +857,7 @@
         <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B16" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B35" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B36" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B38" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -515,7 +515,7 @@
         <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B4" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B5" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B8" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B9" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B12" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -477,7 +477,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B3" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B46" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B2" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B3" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B4" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B5" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B8" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B9" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B12" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B14" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B16" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B17" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B18" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B19" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B21" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B22" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B25" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B27" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B30" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B35" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B36" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B37" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B38" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B40" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B41" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B43" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B44" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B46" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B50" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B52" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B53" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B54" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B57" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>HAUSER - Pavane</v>
       </c>
       <c r="B59" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B64" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B65" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>kenzie - where do we go</v>
       </c>
       <c r="B66" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B68" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B70" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B72" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B75" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B76" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B100" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B2" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B3" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B4" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B5" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B8" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B9" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B12" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B14" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B16" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B17" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B18" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B19" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B21" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B22" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B25" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B27" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B30" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B35" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B36" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B37" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B38" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B40" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B41" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B43" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B44" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B46" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B50" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B52" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B53" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B54" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B57" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>HAUSER - Pavane</v>
       </c>
       <c r="B59" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B64" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B65" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>kenzie - where do we go</v>
       </c>
       <c r="B66" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B68" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B70" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B72" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B75" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B76" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B77" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B78" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B80" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B82" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B96" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B97" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B98" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B99" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B100" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -1541,7 +1541,7 @@
         <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -439,19 +439,19 @@
         <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B2" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1769,19 +1769,19 @@
         <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B37" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2073,19 +2073,19 @@
         <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2339,19 +2339,19 @@
         <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B52" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,19 +2377,19 @@
         <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B53" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4087,19 +4087,19 @@
         <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -781,7 +781,7 @@
         <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B14" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B17" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B18" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B19" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B21" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B22" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B25" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B27" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B30" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B43" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B44" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B50" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -1883,7 +1883,7 @@
         <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B40" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B41" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -2149,7 +2149,7 @@
         <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -857,7 +857,7 @@
         <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B16" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B35" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B36" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B38" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -515,7 +515,7 @@
         <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B4" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B5" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B8" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B9" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B12" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -477,7 +477,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B3" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B46" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G51" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -591,7 +591,7 @@
         <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B2" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B3" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B4" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B5" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B8" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B9" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B12" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B14" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B16" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B17" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B18" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B19" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B21" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B22" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B25" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B27" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B30" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B35" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B36" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B37" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B38" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B40" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B41" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B43" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B44" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B46" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B50" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B52" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B53" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B54" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B57" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>HAUSER - Pavane</v>
       </c>
       <c r="B59" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B64" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B65" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>kenzie - where do we go</v>
       </c>
       <c r="B66" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B68" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B70" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B72" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B75" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B76" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B98" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B99" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B100" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -439,19 +439,19 @@
         <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B2" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,19 +477,19 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B3" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,19 +515,19 @@
         <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B4" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,19 +553,19 @@
         <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B5" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,19 +591,19 @@
         <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,19 +629,19 @@
         <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,19 +667,19 @@
         <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B8" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,19 +705,19 @@
         <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B9" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,19 +743,19 @@
         <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,19 +781,19 @@
         <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,19 +819,19 @@
         <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B12" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,19 +857,19 @@
         <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,19 +895,19 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B14" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,19 +933,19 @@
         <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,19 +971,19 @@
         <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B16" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,19 +1009,19 @@
         <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B17" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,19 +1047,19 @@
         <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B18" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,19 +1085,19 @@
         <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B19" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,19 +1123,19 @@
         <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,19 +1161,19 @@
         <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B21" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,19 +1199,19 @@
         <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B22" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,19 +1237,19 @@
         <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,19 +1275,19 @@
         <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,19 +1313,19 @@
         <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B25" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,19 +1351,19 @@
         <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,19 +1389,19 @@
         <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B27" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,19 +1427,19 @@
         <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,19 +1465,19 @@
         <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,19 +1503,19 @@
         <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B30" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,19 +1541,19 @@
         <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,19 +1579,19 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,19 +1617,19 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,19 +1655,19 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,19 +1693,19 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B35" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,19 +1731,19 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B36" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,19 +1769,19 @@
         <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B37" t="str">
-        <v>10d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>10d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,19 +1807,19 @@
         <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B38" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,19 +1845,19 @@
         <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,19 +1883,19 @@
         <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B40" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,19 +1921,19 @@
         <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B41" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,19 +1959,19 @@
         <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,19 +1997,19 @@
         <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B43" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,19 +2035,19 @@
         <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B44" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,19 +2073,19 @@
         <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>11d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>11d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,19 +2111,19 @@
         <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B46" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,19 +2149,19 @@
         <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,19 +2187,19 @@
         <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,19 +2225,19 @@
         <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,19 +2263,19 @@
         <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B50" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,19 +2301,19 @@
         <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,19 +2339,19 @@
         <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B52" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,19 +2377,19 @@
         <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B53" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,19 +2415,19 @@
         <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B54" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,19 +2453,19 @@
         <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,19 +2491,19 @@
         <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,19 +2529,19 @@
         <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B57" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,19 +2567,19 @@
         <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,19 +2605,19 @@
         <v>HAUSER - Pavane</v>
       </c>
       <c r="B59" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,19 +2643,19 @@
         <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,19 +2681,19 @@
         <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,19 +2719,19 @@
         <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,19 +2757,19 @@
         <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,19 +2795,19 @@
         <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B64" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,19 +2833,19 @@
         <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B65" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,19 +2871,19 @@
         <v>kenzie - where do we go</v>
       </c>
       <c r="B66" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,19 +2909,19 @@
         <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,19 +2947,19 @@
         <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B68" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,19 +2985,19 @@
         <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,19 +3023,19 @@
         <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B70" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,19 +3061,19 @@
         <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,19 +3099,19 @@
         <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B72" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,19 +3137,19 @@
         <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,19 +3175,19 @@
         <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,19 +3213,19 @@
         <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B75" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,19 +3251,19 @@
         <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B76" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,19 +3289,19 @@
         <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B77" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,19 +3327,19 @@
         <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B78" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,19 +3365,19 @@
         <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,19 +3403,19 @@
         <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B80" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,19 +3441,19 @@
         <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,19 +3479,19 @@
         <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B82" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,19 +3517,19 @@
         <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,19 +3555,19 @@
         <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,19 +3593,19 @@
         <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,19 +3631,19 @@
         <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,19 +3669,19 @@
         <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,19 +3707,19 @@
         <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,19 +3745,19 @@
         <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,19 +3783,19 @@
         <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,19 +3821,19 @@
         <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,19 +3859,19 @@
         <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,19 +3897,19 @@
         <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,19 +3935,19 @@
         <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,19 +3973,19 @@
         <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,19 +4011,19 @@
         <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B96" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,19 +4049,19 @@
         <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B97" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,19 +4087,19 @@
         <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B98" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,19 +4125,19 @@
         <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B99" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,19 +4163,19 @@
         <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B100" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,19 +4201,19 @@
         <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B2" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B3" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B4" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B5" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B8" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B9" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B12" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B14" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B16" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B17" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B18" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B19" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B21" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B22" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B25" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B27" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B30" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B35" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B36" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B37" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B38" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B40" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B41" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B43" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B44" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B46" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B50" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B52" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B53" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B54" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B57" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>HAUSER - Pavane</v>
       </c>
       <c r="B59" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B64" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B65" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>kenzie - where do we go</v>
       </c>
       <c r="B66" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B68" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B70" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B72" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B75" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B76" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B98" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B99" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B100" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B2" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B3" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B4" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B5" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B8" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B9" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B12" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B14" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B16" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B17" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B18" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B19" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B21" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B22" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B25" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B27" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B30" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B35" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B36" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B37" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B38" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B40" t="str">
-        <v>11d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>11d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B41" t="str">
-        <v>11d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>11d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B43" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B44" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B46" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B50" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B52" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B53" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B54" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B57" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>HAUSER - Pavane</v>
       </c>
       <c r="B59" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B64" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B65" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>kenzie - where do we go</v>
       </c>
       <c r="B66" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B68" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B70" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B72" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B75" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B76" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B77" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B78" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B80" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B82" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B96" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B97" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B98" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B99" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B100" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -2149,7 +2149,7 @@
         <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -477,7 +477,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B3" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B4" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B5" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B8" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B9" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B12" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B16" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B35" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B36" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B38" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B46" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B96" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -439,19 +439,19 @@
         <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B2" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -781,19 +781,19 @@
         <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -895,19 +895,19 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B14" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1009,19 +1009,19 @@
         <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B17" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,19 +1047,19 @@
         <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B18" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,19 +1085,19 @@
         <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B19" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,19 +1123,19 @@
         <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,19 +1161,19 @@
         <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B21" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,19 +1199,19 @@
         <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B22" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,19 +1237,19 @@
         <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,19 +1275,19 @@
         <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,19 +1313,19 @@
         <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B25" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,19 +1351,19 @@
         <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,19 +1389,19 @@
         <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B27" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,19 +1427,19 @@
         <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,19 +1465,19 @@
         <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,19 +1503,19 @@
         <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B30" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,19 +1541,19 @@
         <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1769,19 +1769,19 @@
         <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B37" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1883,19 +1883,19 @@
         <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B40" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,19 +1921,19 @@
         <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B41" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,19 +1959,19 @@
         <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,19 +1997,19 @@
         <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B43" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,19 +2035,19 @@
         <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B44" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,19 +2073,19 @@
         <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2149,19 +2149,19 @@
         <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3973,19 +3973,19 @@
         <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -477,7 +477,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B3" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B4" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B5" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B8" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B9" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B12" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B16" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B35" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B36" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B38" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B46" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -591,7 +591,7 @@
         <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -3821,7 +3821,7 @@
         <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-04-week04/titles.xlsx
@@ -1541,7 +1541,7 @@
         <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
